--- a/data/nzd0141/nzd0141.xlsx
+++ b/data/nzd0141/nzd0141.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L622"/>
+  <dimension ref="A1:L627"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26568,6 +26568,216 @@
         <v>330.95</v>
       </c>
       <c r="L622" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B623" t="n">
+        <v>315.98</v>
+      </c>
+      <c r="C623" t="n">
+        <v>316.13</v>
+      </c>
+      <c r="D623" t="n">
+        <v>326.88</v>
+      </c>
+      <c r="E623" t="n">
+        <v>335.82</v>
+      </c>
+      <c r="F623" t="n">
+        <v>336.25</v>
+      </c>
+      <c r="G623" t="n">
+        <v>337.43</v>
+      </c>
+      <c r="H623" t="n">
+        <v>343.81</v>
+      </c>
+      <c r="I623" t="n">
+        <v>348.61</v>
+      </c>
+      <c r="J623" t="n">
+        <v>342.17</v>
+      </c>
+      <c r="K623" t="n">
+        <v>330.83</v>
+      </c>
+      <c r="L623" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B624" t="n">
+        <v>316.48</v>
+      </c>
+      <c r="C624" t="n">
+        <v>316</v>
+      </c>
+      <c r="D624" t="n">
+        <v>327.43</v>
+      </c>
+      <c r="E624" t="n">
+        <v>336.66</v>
+      </c>
+      <c r="F624" t="n">
+        <v>336.99</v>
+      </c>
+      <c r="G624" t="n">
+        <v>337.61</v>
+      </c>
+      <c r="H624" t="n">
+        <v>344.26</v>
+      </c>
+      <c r="I624" t="n">
+        <v>350.44</v>
+      </c>
+      <c r="J624" t="n">
+        <v>343.66</v>
+      </c>
+      <c r="K624" t="n">
+        <v>331.33</v>
+      </c>
+      <c r="L624" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B625" t="n">
+        <v>316.49</v>
+      </c>
+      <c r="C625" t="n">
+        <v>315.55</v>
+      </c>
+      <c r="D625" t="n">
+        <v>327.34</v>
+      </c>
+      <c r="E625" t="n">
+        <v>336.68</v>
+      </c>
+      <c r="F625" t="n">
+        <v>337.17</v>
+      </c>
+      <c r="G625" t="n">
+        <v>337.47</v>
+      </c>
+      <c r="H625" t="n">
+        <v>344.44</v>
+      </c>
+      <c r="I625" t="n">
+        <v>350.85</v>
+      </c>
+      <c r="J625" t="n">
+        <v>344.38</v>
+      </c>
+      <c r="K625" t="n">
+        <v>331.67</v>
+      </c>
+      <c r="L625" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B626" t="n">
+        <v>316.2</v>
+      </c>
+      <c r="C626" t="n">
+        <v>315.62</v>
+      </c>
+      <c r="D626" t="n">
+        <v>327.26</v>
+      </c>
+      <c r="E626" t="n">
+        <v>336.39</v>
+      </c>
+      <c r="F626" t="n">
+        <v>336.89</v>
+      </c>
+      <c r="G626" t="n">
+        <v>337.27</v>
+      </c>
+      <c r="H626" t="n">
+        <v>344.05</v>
+      </c>
+      <c r="I626" t="n">
+        <v>350.2</v>
+      </c>
+      <c r="J626" t="n">
+        <v>343.71</v>
+      </c>
+      <c r="K626" t="n">
+        <v>331.56</v>
+      </c>
+      <c r="L626" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B627" t="n">
+        <v>315.54</v>
+      </c>
+      <c r="C627" t="n">
+        <v>315.4</v>
+      </c>
+      <c r="D627" t="n">
+        <v>326.92</v>
+      </c>
+      <c r="E627" t="n">
+        <v>336.12</v>
+      </c>
+      <c r="F627" t="n">
+        <v>336.6</v>
+      </c>
+      <c r="G627" t="n">
+        <v>337.17</v>
+      </c>
+      <c r="H627" t="n">
+        <v>343.69</v>
+      </c>
+      <c r="I627" t="n">
+        <v>349.6</v>
+      </c>
+      <c r="J627" t="n">
+        <v>343.28</v>
+      </c>
+      <c r="K627" t="n">
+        <v>331.49</v>
+      </c>
+      <c r="L627" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26584,7 +26794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B636"/>
+  <dimension ref="A1:B641"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32947,6 +33157,56 @@
       </c>
       <c r="B636" t="n">
         <v>-0.86</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B637" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B638" t="n">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B639" t="n">
+        <v>-1.03</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B640" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B641" t="n">
+        <v>-0.29</v>
       </c>
     </row>
   </sheetData>
@@ -33115,28 +33375,28 @@
         <v>0.0356</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.01410594930319426</v>
+        <v>-0.02135780232902429</v>
       </c>
       <c r="J2" t="n">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="K2" t="n">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0006611221303184367</v>
+        <v>0.001528534352028377</v>
       </c>
       <c r="M2" t="n">
-        <v>3.139225069335922</v>
+        <v>3.143797390626325</v>
       </c>
       <c r="N2" t="n">
-        <v>16.80761165850704</v>
+        <v>16.83111150471419</v>
       </c>
       <c r="O2" t="n">
-        <v>4.099708728496092</v>
+        <v>4.102573765907712</v>
       </c>
       <c r="P2" t="n">
-        <v>321.0086567713009</v>
+        <v>321.0849350887892</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33193,28 +33453,28 @@
         <v>0.0512</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04479591965479528</v>
+        <v>0.03867655352360783</v>
       </c>
       <c r="J3" t="n">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="K3" t="n">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00755771444613984</v>
+        <v>0.005707499523105453</v>
       </c>
       <c r="M3" t="n">
-        <v>3.098629362044883</v>
+        <v>3.100252159409477</v>
       </c>
       <c r="N3" t="n">
-        <v>14.72522619540531</v>
+        <v>14.71983802293312</v>
       </c>
       <c r="O3" t="n">
-        <v>3.837346243878093</v>
+        <v>3.836644109496361</v>
       </c>
       <c r="P3" t="n">
-        <v>318.3258319254183</v>
+        <v>318.3901995587543</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33271,28 +33531,28 @@
         <v>0.046</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0565025495592236</v>
+        <v>-0.05980763335597537</v>
       </c>
       <c r="J4" t="n">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="K4" t="n">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01320856282037919</v>
+        <v>0.01501438169430813</v>
       </c>
       <c r="M4" t="n">
-        <v>2.964410519057626</v>
+        <v>2.95634272569799</v>
       </c>
       <c r="N4" t="n">
-        <v>13.32834345233055</v>
+        <v>13.25485218327274</v>
       </c>
       <c r="O4" t="n">
-        <v>3.65080038516632</v>
+        <v>3.640721382263786</v>
       </c>
       <c r="P4" t="n">
-        <v>330.7315452639871</v>
+        <v>330.7663085872085</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33349,28 +33609,28 @@
         <v>0.0417</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.09650881234094022</v>
+        <v>-0.1000957444697996</v>
       </c>
       <c r="J5" t="n">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="K5" t="n">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03499966645622055</v>
+        <v>0.03813337535857242</v>
       </c>
       <c r="M5" t="n">
-        <v>2.835748583223595</v>
+        <v>2.829266938828461</v>
       </c>
       <c r="N5" t="n">
-        <v>14.3505246657191</v>
+        <v>14.27512935683953</v>
       </c>
       <c r="O5" t="n">
-        <v>3.788208635452791</v>
+        <v>3.778244216145844</v>
       </c>
       <c r="P5" t="n">
-        <v>341.1477422658701</v>
+        <v>341.1854692107844</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33427,28 +33687,28 @@
         <v>0.0408</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.075640397620724</v>
+        <v>-0.08001654347609803</v>
       </c>
       <c r="J6" t="n">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="K6" t="n">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0233837325199403</v>
+        <v>0.02646370151421196</v>
       </c>
       <c r="M6" t="n">
-        <v>2.879941581925236</v>
+        <v>2.878139061364053</v>
       </c>
       <c r="N6" t="n">
-        <v>13.35328151974931</v>
+        <v>13.30455491590024</v>
       </c>
       <c r="O6" t="n">
-        <v>3.654214213719457</v>
+        <v>3.647540940949154</v>
       </c>
       <c r="P6" t="n">
-        <v>341.5249434399115</v>
+        <v>341.5709709008172</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33505,28 +33765,28 @@
         <v>0.0371</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.07332166772695985</v>
+        <v>-0.07833105289304197</v>
       </c>
       <c r="J7" t="n">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="K7" t="n">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02113361483119292</v>
+        <v>0.02436320781596513</v>
       </c>
       <c r="M7" t="n">
-        <v>2.894296656496561</v>
+        <v>2.899266797272412</v>
       </c>
       <c r="N7" t="n">
-        <v>13.91989395700692</v>
+        <v>13.88358839728095</v>
       </c>
       <c r="O7" t="n">
-        <v>3.730937409955696</v>
+        <v>3.726068759065102</v>
       </c>
       <c r="P7" t="n">
-        <v>342.462625203218</v>
+        <v>342.5153384011656</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33583,28 +33843,28 @@
         <v>0.0403</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.02306769288213469</v>
+        <v>-0.02301708278104358</v>
       </c>
       <c r="J8" t="n">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="K8" t="n">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003120377755928438</v>
+        <v>0.003165214641644987</v>
       </c>
       <c r="M8" t="n">
-        <v>2.328780691233035</v>
+        <v>2.312164684518798</v>
       </c>
       <c r="N8" t="n">
-        <v>9.499793081226603</v>
+        <v>9.424532035761684</v>
       </c>
       <c r="O8" t="n">
-        <v>3.082173434644229</v>
+        <v>3.069940070386014</v>
       </c>
       <c r="P8" t="n">
-        <v>344.6384127512755</v>
+        <v>344.6378818594659</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33661,28 +33921,28 @@
         <v>0.046</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0165599005428585</v>
+        <v>0.01940833573081143</v>
       </c>
       <c r="J9" t="n">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="K9" t="n">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001330923621882918</v>
+        <v>0.001857097142751618</v>
       </c>
       <c r="M9" t="n">
-        <v>2.565029391433903</v>
+        <v>2.560314405579512</v>
       </c>
       <c r="N9" t="n">
-        <v>11.49884438423543</v>
+        <v>11.43599378525668</v>
       </c>
       <c r="O9" t="n">
-        <v>3.39099460103307</v>
+        <v>3.381714622089907</v>
       </c>
       <c r="P9" t="n">
-        <v>347.7314185576731</v>
+        <v>347.7014555041002</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33739,28 +33999,28 @@
         <v>0.0509</v>
       </c>
       <c r="I10" t="n">
-        <v>0.02614463774917922</v>
+        <v>0.02850501042954708</v>
       </c>
       <c r="J10" t="n">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="K10" t="n">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="L10" t="n">
-        <v>0.003213029557605052</v>
+        <v>0.00388224286160177</v>
       </c>
       <c r="M10" t="n">
-        <v>2.788827462299735</v>
+        <v>2.775609025114506</v>
       </c>
       <c r="N10" t="n">
-        <v>11.85013146937586</v>
+        <v>11.77632025024019</v>
       </c>
       <c r="O10" t="n">
-        <v>3.442401991252018</v>
+        <v>3.431664355708493</v>
       </c>
       <c r="P10" t="n">
-        <v>341.2757300509767</v>
+        <v>341.2508993958833</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33817,28 +34077,28 @@
         <v>0.0522</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0271036320252348</v>
+        <v>-0.02954286205874778</v>
       </c>
       <c r="J11" t="n">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="K11" t="n">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="L11" t="n">
-        <v>0.003159850426287303</v>
+        <v>0.003817319626971294</v>
       </c>
       <c r="M11" t="n">
-        <v>2.917613298605555</v>
+        <v>2.905871004052095</v>
       </c>
       <c r="N11" t="n">
-        <v>12.95043213806228</v>
+        <v>12.86544498414325</v>
       </c>
       <c r="O11" t="n">
-        <v>3.598670884932696</v>
+        <v>3.586843317478929</v>
       </c>
       <c r="P11" t="n">
-        <v>333.6157622167364</v>
+        <v>333.641414953307</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33876,7 +34136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L622"/>
+  <dimension ref="A1:L627"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72439,6 +72699,316 @@
         </is>
       </c>
     </row>
+    <row r="623">
+      <c r="A623" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>-36.60177278075409,174.70833553361405</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>-36.60243981498949,174.70867693876514</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>-36.603076897759195,174.70913135457164</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>-36.6037085493373,174.7096122073367</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>-36.60433871930829,174.7100727262108</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>-36.604957366641074,174.7105348485802</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>-36.60555116685996,174.7110490123741</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>-36.606156013330335,174.7115541183116</t>
+        </is>
+      </c>
+      <c r="J623" t="inlineStr">
+        <is>
+          <t>-36.60677260671797,174.71204240581653</t>
+        </is>
+      </c>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>-36.60740829909872,174.7124902880768</t>
+        </is>
+      </c>
+      <c r="L623" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>-36.601771029973555,174.70834068340372</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>-36.602440270195046,174.70867559980988</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>-36.60307485481863,174.7091369559875</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>-36.60370496271251,174.70962047621916</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>-36.60433531106231,174.71007983626677</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>-36.60495653577849,174.71053657671538</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>-36.605549080000955,174.71105332554495</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>-36.6061467107301,174.71157101007444</t>
+        </is>
+      </c>
+      <c r="J624" t="inlineStr">
+        <is>
+          <t>-36.6067643617343,174.71205555250506</t>
+        </is>
+      </c>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>-36.60740551636193,174.71249468427823</t>
+        </is>
+      </c>
+      <c r="L624" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>-36.601770994957946,174.70834078639953</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>-36.60244184590645,174.70867096496448</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>-36.603075189118016,174.7091360393922</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>-36.60370487731666,174.7096206730973</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>-36.60433448202943,174.71008156573973</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>-36.60495718200495,174.71053523261025</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>-36.60554824525731,174.71105505081323</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>-36.60614462654066,174.7115747945672</t>
+        </is>
+      </c>
+      <c r="J625" t="inlineStr">
+        <is>
+          <t>-36.60676037758062,174.71206190526627</t>
+        </is>
+      </c>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>-36.60740362410081,174.71249767369505</t>
+        </is>
+      </c>
+      <c r="L625" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>-36.60177201041067,174.70833779952153</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>-36.6024416007958,174.70867168594043</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>-36.60307548627302,174.70913522464082</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>-36.603706115556236,174.70961781836417</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>-36.604335771636116,174.7100788754484</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>-36.60495810518556,174.71053331246003</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>-36.60555005386851,174.71105131273194</t>
+        </is>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>-36.606147930743376,174.71156879476152</t>
+        </is>
+      </c>
+      <c r="J626" t="inlineStr">
+        <is>
+          <t>-36.60676408505697,174.71205599366905</t>
+        </is>
+      </c>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>-36.60740423630295,174.7124967065308</t>
+        </is>
+      </c>
+      <c r="L626" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>-36.60177432144077,174.70833100179897</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>-36.602442371143546,174.70866942001598</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>-36.60307674918172,174.70913176194733</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>-36.60370726839992,174.70961516050912</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>-36.60433710730012,174.71007608907516</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>-36.60495856677587,174.7105323523849</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>-36.60555172335567,174.7110478621952</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>-36.6061509807764,174.7115632564789</t>
+        </is>
+      </c>
+      <c r="J627" t="inlineStr">
+        <is>
+          <t>-36.60676646448194,174.7120521996586</t>
+        </is>
+      </c>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>-36.60740462588611,174.71249609106263</t>
+        </is>
+      </c>
+      <c r="L627" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0141/nzd0141.xlsx
+++ b/data/nzd0141/nzd0141.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L627"/>
+  <dimension ref="A1:L629"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26778,6 +26778,90 @@
         <v>331.49</v>
       </c>
       <c r="L627" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B628" t="n">
+        <v>315.63</v>
+      </c>
+      <c r="C628" t="n">
+        <v>315.79</v>
+      </c>
+      <c r="D628" t="n">
+        <v>327.17</v>
+      </c>
+      <c r="E628" t="n">
+        <v>336.44</v>
+      </c>
+      <c r="F628" t="n">
+        <v>336.9</v>
+      </c>
+      <c r="G628" t="n">
+        <v>337.61</v>
+      </c>
+      <c r="H628" t="n">
+        <v>343.93</v>
+      </c>
+      <c r="I628" t="n">
+        <v>349.74</v>
+      </c>
+      <c r="J628" t="n">
+        <v>343.23</v>
+      </c>
+      <c r="K628" t="n">
+        <v>333.54</v>
+      </c>
+      <c r="L628" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B629" t="n">
+        <v>315.4</v>
+      </c>
+      <c r="C629" t="n">
+        <v>315.96</v>
+      </c>
+      <c r="D629" t="n">
+        <v>327.55</v>
+      </c>
+      <c r="E629" t="n">
+        <v>336.96</v>
+      </c>
+      <c r="F629" t="n">
+        <v>337.42</v>
+      </c>
+      <c r="G629" t="n">
+        <v>338.26</v>
+      </c>
+      <c r="H629" t="n">
+        <v>344.2</v>
+      </c>
+      <c r="I629" t="n">
+        <v>350.29</v>
+      </c>
+      <c r="J629" t="n">
+        <v>343.63</v>
+      </c>
+      <c r="K629" t="n">
+        <v>333.97</v>
+      </c>
+      <c r="L629" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26794,7 +26878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B641"/>
+  <dimension ref="A1:B643"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33207,6 +33291,26 @@
       </c>
       <c r="B641" t="n">
         <v>-0.29</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B642" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B643" t="n">
+        <v>-0.14</v>
       </c>
     </row>
   </sheetData>
@@ -33375,28 +33479,28 @@
         <v>0.0356</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02135780232902429</v>
+        <v>-0.02457374266403334</v>
       </c>
       <c r="J2" t="n">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="K2" t="n">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001528534352028377</v>
+        <v>0.002028060374203777</v>
       </c>
       <c r="M2" t="n">
-        <v>3.143797390626325</v>
+        <v>3.146899463840889</v>
       </c>
       <c r="N2" t="n">
-        <v>16.83111150471419</v>
+        <v>16.85622446168651</v>
       </c>
       <c r="O2" t="n">
-        <v>4.102573765907712</v>
+        <v>4.105633259521181</v>
       </c>
       <c r="P2" t="n">
-        <v>321.0849350887892</v>
+        <v>321.1188698057549</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33453,28 +33557,28 @@
         <v>0.0512</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03867655352360783</v>
+        <v>0.03638570497074166</v>
       </c>
       <c r="J3" t="n">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="K3" t="n">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005707499523105453</v>
+        <v>0.005078460808978336</v>
       </c>
       <c r="M3" t="n">
-        <v>3.100252159409477</v>
+        <v>3.100202882291533</v>
       </c>
       <c r="N3" t="n">
-        <v>14.71983802293312</v>
+        <v>14.71290932240915</v>
       </c>
       <c r="O3" t="n">
-        <v>3.836644109496361</v>
+        <v>3.835741039539707</v>
       </c>
       <c r="P3" t="n">
-        <v>318.3901995587543</v>
+        <v>318.4143717249787</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33531,28 +33635,28 @@
         <v>0.046</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.05980763335597537</v>
+        <v>-0.06096197239718364</v>
       </c>
       <c r="J4" t="n">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="K4" t="n">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01501438169430813</v>
+        <v>0.0156928711060017</v>
       </c>
       <c r="M4" t="n">
-        <v>2.95634272569799</v>
+        <v>2.952393845774921</v>
       </c>
       <c r="N4" t="n">
-        <v>13.25485218327274</v>
+        <v>13.22289306736465</v>
       </c>
       <c r="O4" t="n">
-        <v>3.640721382263786</v>
+        <v>3.636329614785305</v>
       </c>
       <c r="P4" t="n">
-        <v>330.7663085872085</v>
+        <v>330.778487901716</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33609,28 +33713,28 @@
         <v>0.0417</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1000957444697996</v>
+        <v>-0.1012447189295914</v>
       </c>
       <c r="J5" t="n">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="K5" t="n">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03813337535857242</v>
+        <v>0.03923158998733767</v>
       </c>
       <c r="M5" t="n">
-        <v>2.829266938828461</v>
+        <v>2.825550352690983</v>
       </c>
       <c r="N5" t="n">
-        <v>14.27512935683953</v>
+        <v>14.2399284305722</v>
       </c>
       <c r="O5" t="n">
-        <v>3.778244216145844</v>
+        <v>3.773582969880508</v>
       </c>
       <c r="P5" t="n">
-        <v>341.1854692107844</v>
+        <v>341.197591518106</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33687,28 +33791,28 @@
         <v>0.0408</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.08001654347609803</v>
+        <v>-0.08146668579484424</v>
       </c>
       <c r="J6" t="n">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="K6" t="n">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02646370151421196</v>
+        <v>0.02757097034147249</v>
       </c>
       <c r="M6" t="n">
-        <v>2.878139061364053</v>
+        <v>2.876021700777493</v>
       </c>
       <c r="N6" t="n">
-        <v>13.30455491590024</v>
+        <v>13.27841399207478</v>
       </c>
       <c r="O6" t="n">
-        <v>3.647540940949154</v>
+        <v>3.643955816427359</v>
       </c>
       <c r="P6" t="n">
-        <v>341.5709709008172</v>
+        <v>341.5862710373848</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33765,28 +33869,28 @@
         <v>0.0371</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.07833105289304197</v>
+        <v>-0.07992046774708625</v>
       </c>
       <c r="J7" t="n">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="K7" t="n">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02436320781596513</v>
+        <v>0.02548550058173038</v>
       </c>
       <c r="M7" t="n">
-        <v>2.899266797272412</v>
+        <v>2.898889356681209</v>
       </c>
       <c r="N7" t="n">
-        <v>13.88358839728095</v>
+        <v>13.85888100007275</v>
       </c>
       <c r="O7" t="n">
-        <v>3.726068759065102</v>
+        <v>3.722751804790746</v>
       </c>
       <c r="P7" t="n">
-        <v>342.5153384011656</v>
+        <v>342.5321150138526</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33843,28 +33947,28 @@
         <v>0.0403</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.02301708278104358</v>
+        <v>-0.0229870924127721</v>
       </c>
       <c r="J8" t="n">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="K8" t="n">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003165214641644987</v>
+        <v>0.003180441171523163</v>
       </c>
       <c r="M8" t="n">
-        <v>2.312164684518798</v>
+        <v>2.305248629134905</v>
       </c>
       <c r="N8" t="n">
-        <v>9.424532035761684</v>
+        <v>9.394583061579089</v>
       </c>
       <c r="O8" t="n">
-        <v>3.069940070386014</v>
+        <v>3.065058410794008</v>
       </c>
       <c r="P8" t="n">
-        <v>344.6378818594659</v>
+        <v>344.6375646318119</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33921,28 +34025,28 @@
         <v>0.046</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01940833573081143</v>
+        <v>0.02056260543089452</v>
       </c>
       <c r="J9" t="n">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="K9" t="n">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001857097142751618</v>
+        <v>0.002097689294696781</v>
       </c>
       <c r="M9" t="n">
-        <v>2.560314405579512</v>
+        <v>2.558507415698315</v>
       </c>
       <c r="N9" t="n">
-        <v>11.43599378525668</v>
+        <v>11.40994086598678</v>
       </c>
       <c r="O9" t="n">
-        <v>3.381714622089907</v>
+        <v>3.377860397646235</v>
       </c>
       <c r="P9" t="n">
-        <v>347.7014555041002</v>
+        <v>347.6892742899303</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33999,28 +34103,28 @@
         <v>0.0509</v>
       </c>
       <c r="I10" t="n">
-        <v>0.02850501042954708</v>
+        <v>0.02941159390971664</v>
       </c>
       <c r="J10" t="n">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="K10" t="n">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="L10" t="n">
-        <v>0.00388224286160177</v>
+        <v>0.004160509168097515</v>
       </c>
       <c r="M10" t="n">
-        <v>2.775609025114506</v>
+        <v>2.770231148418333</v>
       </c>
       <c r="N10" t="n">
-        <v>11.77632025024019</v>
+        <v>11.74519485603073</v>
       </c>
       <c r="O10" t="n">
-        <v>3.431664355708493</v>
+        <v>3.427126326243421</v>
       </c>
       <c r="P10" t="n">
-        <v>341.2508993958833</v>
+        <v>341.2413321312254</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34077,28 +34181,28 @@
         <v>0.0522</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.02954286205874778</v>
+        <v>-0.02895768708892166</v>
       </c>
       <c r="J11" t="n">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="K11" t="n">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="L11" t="n">
-        <v>0.003817319626971294</v>
+        <v>0.003694604069287788</v>
       </c>
       <c r="M11" t="n">
-        <v>2.905871004052095</v>
+        <v>2.899599757095237</v>
       </c>
       <c r="N11" t="n">
-        <v>12.86544498414325</v>
+        <v>12.82722058103954</v>
       </c>
       <c r="O11" t="n">
-        <v>3.586843317478929</v>
+        <v>3.58151093549071</v>
       </c>
       <c r="P11" t="n">
-        <v>333.641414953307</v>
+        <v>333.6352390673009</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34136,7 +34240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L627"/>
+  <dimension ref="A1:L629"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73009,6 +73113,130 @@
         </is>
       </c>
     </row>
+    <row r="628">
+      <c r="A628" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>-36.601774006300325,174.70833192876117</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>-36.60244100552705,174.70867343688207</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>-36.60307582057239,174.7091343080455</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>-36.603705902066665,174.70961831055953</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>-36.604335725578736,174.71007897153024</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>-36.60495653577849,174.71053657671538</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>-36.60555061036425,174.71105016255305</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>-36.60615026910205,174.7115645487449</t>
+        </is>
+      </c>
+      <c r="J628" t="inlineStr">
+        <is>
+          <t>-36.60676674115926,174.71205175849454</t>
+        </is>
+      </c>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>-36.6073932166634,174.71251411548477</t>
+        </is>
+      </c>
+      <c r="L628" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>-36.60177481165922,174.70832955985776</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>-36.60244041025829,174.70867518782362</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>-36.60307440908611,174.70913817811456</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>-36.603703681774945,174.70962342939126</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>-36.60433333059485,174.71008396778547</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>-36.604953535441204,174.7105428172032</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>-36.60554935824883,174.71105275045554</t>
+        </is>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>-36.60614747323841,174.71156962550387</t>
+        </is>
+      </c>
+      <c r="J629" t="inlineStr">
+        <is>
+          <t>-36.6067645277407,174.71205528780663</t>
+        </is>
+      </c>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>-36.60739082350905,174.71251789621653</t>
+        </is>
+      </c>
+      <c r="L629" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0141/nzd0141.xlsx
+++ b/data/nzd0141/nzd0141.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L629"/>
+  <dimension ref="A1:L630"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26862,6 +26862,48 @@
         <v>333.97</v>
       </c>
       <c r="L629" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B630" t="n">
+        <v>316.09</v>
+      </c>
+      <c r="C630" t="n">
+        <v>316.32</v>
+      </c>
+      <c r="D630" t="n">
+        <v>328.09</v>
+      </c>
+      <c r="E630" t="n">
+        <v>337.65</v>
+      </c>
+      <c r="F630" t="n">
+        <v>338.12</v>
+      </c>
+      <c r="G630" t="n">
+        <v>339.2</v>
+      </c>
+      <c r="H630" t="n">
+        <v>344.63</v>
+      </c>
+      <c r="I630" t="n">
+        <v>350.51</v>
+      </c>
+      <c r="J630" t="n">
+        <v>343.84</v>
+      </c>
+      <c r="K630" t="n">
+        <v>334.14</v>
+      </c>
+      <c r="L630" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26878,7 +26920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B643"/>
+  <dimension ref="A1:B644"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33311,6 +33353,16 @@
       </c>
       <c r="B643" t="n">
         <v>-0.14</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B644" t="n">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>
@@ -33479,28 +33531,28 @@
         <v>0.0356</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02457374266403334</v>
+        <v>-0.02598081963996612</v>
       </c>
       <c r="J2" t="n">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="K2" t="n">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002028060374203777</v>
+        <v>0.002270826313136798</v>
       </c>
       <c r="M2" t="n">
-        <v>3.146899463840889</v>
+        <v>3.14761381104294</v>
       </c>
       <c r="N2" t="n">
-        <v>16.85622446168651</v>
+        <v>16.85951620126547</v>
       </c>
       <c r="O2" t="n">
-        <v>4.105633259521181</v>
+        <v>4.106034120811159</v>
       </c>
       <c r="P2" t="n">
-        <v>321.1188698057549</v>
+        <v>321.133770670897</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33557,28 +33609,28 @@
         <v>0.0512</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03638570497074166</v>
+        <v>0.03539405941393367</v>
       </c>
       <c r="J3" t="n">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="K3" t="n">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005078460808978336</v>
+        <v>0.004819744039121665</v>
       </c>
       <c r="M3" t="n">
-        <v>3.100202882291533</v>
+        <v>3.099493295511931</v>
       </c>
       <c r="N3" t="n">
-        <v>14.71290932240915</v>
+        <v>14.70446358357691</v>
       </c>
       <c r="O3" t="n">
-        <v>3.835741039539707</v>
+        <v>3.834639954881932</v>
       </c>
       <c r="P3" t="n">
-        <v>318.4143717249787</v>
+        <v>318.4248731950215</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33635,28 +33687,28 @@
         <v>0.046</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.06096197239718364</v>
+        <v>-0.06129673602028362</v>
       </c>
       <c r="J4" t="n">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="K4" t="n">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0156928711060017</v>
+        <v>0.01591932146922126</v>
       </c>
       <c r="M4" t="n">
-        <v>2.952393845774921</v>
+        <v>2.949269799099104</v>
       </c>
       <c r="N4" t="n">
-        <v>13.22289306736465</v>
+        <v>13.20357418008243</v>
       </c>
       <c r="O4" t="n">
-        <v>3.636329614785305</v>
+        <v>3.633672271969836</v>
       </c>
       <c r="P4" t="n">
-        <v>330.778487901716</v>
+        <v>330.7820330294436</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33713,28 +33765,28 @@
         <v>0.0417</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1012447189295914</v>
+        <v>-0.1015058870679663</v>
       </c>
       <c r="J5" t="n">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="K5" t="n">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03923158998733767</v>
+        <v>0.03956512762291653</v>
       </c>
       <c r="M5" t="n">
-        <v>2.825550352690983</v>
+        <v>2.822249480156698</v>
       </c>
       <c r="N5" t="n">
-        <v>14.2399284305722</v>
+        <v>14.21832607852686</v>
       </c>
       <c r="O5" t="n">
-        <v>3.773582969880508</v>
+        <v>3.770719570390625</v>
       </c>
       <c r="P5" t="n">
-        <v>341.197591518106</v>
+        <v>341.2003572738364</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33791,28 +33843,28 @@
         <v>0.0408</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.08146668579484424</v>
+        <v>-0.08187227777346044</v>
       </c>
       <c r="J6" t="n">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="K6" t="n">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02757097034147249</v>
+        <v>0.0279346209418494</v>
       </c>
       <c r="M6" t="n">
-        <v>2.876021700777493</v>
+        <v>2.873401590581585</v>
       </c>
       <c r="N6" t="n">
-        <v>13.27841399207478</v>
+        <v>13.25980379659493</v>
       </c>
       <c r="O6" t="n">
-        <v>3.643955816427359</v>
+        <v>3.641401350660887</v>
       </c>
       <c r="P6" t="n">
-        <v>341.5862710373848</v>
+        <v>341.5905662333687</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33869,28 +33921,28 @@
         <v>0.0371</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.07992046774708625</v>
+        <v>-0.08029887100667925</v>
       </c>
       <c r="J7" t="n">
+        <v>629</v>
+      </c>
+      <c r="K7" t="n">
         <v>628</v>
       </c>
-      <c r="K7" t="n">
-        <v>627</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.02548550058173038</v>
+        <v>0.02581089619471688</v>
       </c>
       <c r="M7" t="n">
-        <v>2.898889356681209</v>
+        <v>2.896365739360685</v>
       </c>
       <c r="N7" t="n">
-        <v>13.85888100007275</v>
+        <v>13.83899087032198</v>
       </c>
       <c r="O7" t="n">
-        <v>3.722751804790746</v>
+        <v>3.720079417206303</v>
       </c>
       <c r="P7" t="n">
-        <v>342.5321150138526</v>
+        <v>342.5361240349231</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33947,28 +33999,28 @@
         <v>0.0403</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0229870924127721</v>
+        <v>-0.02278741027379848</v>
       </c>
       <c r="J8" t="n">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="K8" t="n">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003180441171523163</v>
+        <v>0.003137050357870153</v>
       </c>
       <c r="M8" t="n">
-        <v>2.305248629134905</v>
+        <v>2.3026636329048</v>
       </c>
       <c r="N8" t="n">
-        <v>9.394583061579089</v>
+        <v>9.380253310484589</v>
       </c>
       <c r="O8" t="n">
-        <v>3.065058410794008</v>
+        <v>3.062719920346062</v>
       </c>
       <c r="P8" t="n">
-        <v>344.6375646318119</v>
+        <v>344.6354500093179</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34025,28 +34077,28 @@
         <v>0.046</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02056260543089452</v>
+        <v>0.02129254009877984</v>
       </c>
       <c r="J9" t="n">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="K9" t="n">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002097689294696781</v>
+        <v>0.002255713116380287</v>
       </c>
       <c r="M9" t="n">
-        <v>2.558507415698315</v>
+        <v>2.5584383123926</v>
       </c>
       <c r="N9" t="n">
-        <v>11.40994086598678</v>
+        <v>11.399898671397</v>
       </c>
       <c r="O9" t="n">
-        <v>3.377860397646235</v>
+        <v>3.376373597722415</v>
       </c>
       <c r="P9" t="n">
-        <v>347.6892742899303</v>
+        <v>347.6815443233153</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34103,28 +34155,28 @@
         <v>0.0509</v>
       </c>
       <c r="I10" t="n">
-        <v>0.02941159390971664</v>
+        <v>0.02999217036482072</v>
       </c>
       <c r="J10" t="n">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="K10" t="n">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="L10" t="n">
-        <v>0.004160509168097515</v>
+        <v>0.004339889263401675</v>
       </c>
       <c r="M10" t="n">
-        <v>2.770231148418333</v>
+        <v>2.768020977532886</v>
       </c>
       <c r="N10" t="n">
-        <v>11.74519485603073</v>
+        <v>11.73164485770651</v>
       </c>
       <c r="O10" t="n">
-        <v>3.427126326243421</v>
+        <v>3.425148881100866</v>
       </c>
       <c r="P10" t="n">
-        <v>341.2413321312254</v>
+        <v>341.2351838595884</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34181,28 +34233,28 @@
         <v>0.0522</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.02895768708892166</v>
+        <v>-0.02854281550646023</v>
       </c>
       <c r="J11" t="n">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="K11" t="n">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="L11" t="n">
-        <v>0.003694604069287788</v>
+        <v>0.003602521981545093</v>
       </c>
       <c r="M11" t="n">
-        <v>2.899599757095237</v>
+        <v>2.897086984542494</v>
       </c>
       <c r="N11" t="n">
-        <v>12.82722058103954</v>
+        <v>12.80944341605317</v>
       </c>
       <c r="O11" t="n">
-        <v>3.58151093549071</v>
+        <v>3.579028278185739</v>
       </c>
       <c r="P11" t="n">
-        <v>333.6352390673009</v>
+        <v>333.6308456008401</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34240,7 +34292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L629"/>
+  <dimension ref="A1:L630"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73237,6 +73289,68 @@
         </is>
       </c>
     </row>
+    <row r="630">
+      <c r="A630" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>-36.60177239558239,174.70833666656782</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>-36.60243914968905,174.7086788956998</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>-36.60307240328962,174.70914367768611</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>-36.60370073561829,174.7096302216867</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>-36.60433010657777,174.71009069351314</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>-36.604949196491326,174.7105518419078</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>-36.605547364139,174.71105687192969</t>
+        </is>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>-36.60614635489289,174.71157165620738</t>
+        </is>
+      </c>
+      <c r="J630" t="inlineStr">
+        <is>
+          <t>-36.6067633656959,174.7120571406954</t>
+        </is>
+      </c>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>-36.607389877378225,174.71251939092434</t>
+        </is>
+      </c>
+      <c r="L630" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
